--- a/output/pdf_financials_xlsx/CS.xlsx
+++ b/output/pdf_financials_xlsx/CS.xlsx
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>36.660765</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>43.301039</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -28206,7 +28206,11 @@
           <t>Selling, general and administrative costs</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -28218,10 +28222,10 @@
         </is>
       </c>
       <c r="G429" s="5" t="n">
-        <v>-36.660765</v>
+        <v>36.660765</v>
       </c>
       <c r="H429" s="5" t="n">
-        <v>-43.301039</v>
+        <v>43.301039</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
